--- a/output/pdf_financials_xlsx/GAL.xlsx
+++ b/output/pdf_financials_xlsx/GAL.xlsx
@@ -6359,52 +6359,52 @@
         <v>3.962831</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>4.069045</v>
+        <v>4.009841</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>4.781439</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>5.440196</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>6.25346</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>6.60433</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>8.478946000000001</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>7.026057</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>7.658187</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>8.963163</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>9.416411999999999</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>9.734121</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>15.435369</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>15.515105</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>18.579467</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>20.1485</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>25.03502</v>
       </c>
     </row>
     <row r="93">
@@ -12132,7 +12132,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -15126,7 +15130,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -18460,7 +18468,11 @@
           <t>Reserves 5,258,030</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GAL.xlsx
+++ b/output/pdf_financials_xlsx/GAL.xlsx
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000149</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.45222</v>
+        <v>-2.452071</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-6.361697</v>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.893541</v>
+        <v>-0.893392</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-4.695005</v>
@@ -2725,31 +2725,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.587489</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.485997</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.485997</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.661798</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.164868</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.166617</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.020259</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.518332</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.557005</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0.779758</v>
@@ -2847,31 +2847,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.587489</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.485997</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.485997</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>2.661798</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.164868</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.166617</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.020259</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.518332</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.557005</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0.779758</v>
@@ -3579,31 +3579,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.917956</v>
+        <v>0.330467</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.143512</v>
+        <v>0.657515</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.143512</v>
+        <v>0.657515</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3.413031</v>
+        <v>0.751233</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.837922</v>
+        <v>0.673054</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.5717410000000001</v>
+        <v>0.405124</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.122472</v>
+        <v>0.102213</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.767991</v>
+        <v>0.249659</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.663737</v>
+        <v>0.106732</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.31641</v>
@@ -15822,7 +15822,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -16656,7 +16656,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -18898,7 +18898,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
@@ -44594,7 +44594,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E339" s="5" t="n">

--- a/output/pdf_financials_xlsx/GAL.xlsx
+++ b/output/pdf_financials_xlsx/GAL.xlsx
@@ -832,52 +832,52 @@
         <v>0.103383</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.110765</v>
+        <v>0.159192</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.255181</v>
+        <v>0.294181</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.27632</v>
+        <v>0.30592</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.169809</v>
+        <v>0.197559</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.205248</v>
+        <v>0.232498</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.238643</v>
+        <v>0.267393</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.262428</v>
+        <v>0.288928</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.235456</v>
+        <v>0.261956</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.194992</v>
+        <v>0.224242</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.209903</v>
+        <v>0.245403</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.198513</v>
+        <v>0.233513</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.41959</v>
+        <v>0.519007</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.50609</v>
+        <v>0.6460900000000001</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.478059</v>
+        <v>0.618059</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.288271</v>
+        <v>0.443271</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.380662</v>
+        <v>0.520662</v>
       </c>
     </row>
     <row r="8">
@@ -2917,46 +2917,46 @@
         <v>0</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0</v>
+        <v>0.690433</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0</v>
+        <v>0.258504</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0</v>
+        <v>0.202205</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0</v>
+        <v>0.035999</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0</v>
+        <v>0.062725</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0</v>
+        <v>0.013206</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>0</v>
+        <v>0.00318</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0</v>
+        <v>0.109927</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>0</v>
+        <v>0.250533</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>0</v>
+        <v>0.29551</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>0</v>
+        <v>0.594071</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0</v>
+        <v>0.116374</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>0</v>
+        <v>0.08326600000000001</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>0</v>
+        <v>0.06980600000000001</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>0</v>
@@ -3161,46 +3161,46 @@
         <v>0</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0</v>
+        <v>0.690433</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0</v>
+        <v>0.258504</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0</v>
+        <v>0.202205</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0</v>
+        <v>0.035999</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0</v>
+        <v>0.062725</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0</v>
+        <v>0.013206</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0</v>
+        <v>0.00318</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0</v>
+        <v>0.109927</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>0</v>
+        <v>0.250533</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>0</v>
+        <v>0.29551</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>0</v>
+        <v>0.594071</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0</v>
+        <v>0.116374</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>0</v>
+        <v>0.08326600000000001</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>0</v>
+        <v>0.06980600000000001</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>0</v>
@@ -3588,46 +3588,46 @@
         <v>0.657515</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.751233</v>
+        <v>0.0608</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.673054</v>
+        <v>0.41455</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.405124</v>
+        <v>0.202919</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.102213</v>
+        <v>0.066214</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.249659</v>
+        <v>0.186934</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.106732</v>
+        <v>0.093526</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.31641</v>
+        <v>0.31323</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.287273</v>
+        <v>0.177346</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.416699</v>
+        <v>0.166166</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.59496</v>
+        <v>0.29945</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.279935</v>
+        <v>0.685864</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>1.810993</v>
+        <v>1.694619</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>1.59688</v>
+        <v>1.513614</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.364362</v>
+        <v>0.294556</v>
       </c>
       <c r="S48" s="3" t="n">
         <v>0.228522</v>
@@ -4794,46 +4794,46 @@
         <v>0</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.856321</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.671803</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.562963</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.63208</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.557449</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.574724</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>1.23939</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>1.047141</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.926512</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>1.550683</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>1.523796</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>1.531585</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>1.421166</v>
       </c>
       <c r="S67" s="3" t="n">
-        <v>0</v>
+        <v>0.491473</v>
       </c>
     </row>
     <row r="68">
@@ -4855,46 +4855,46 @@
         <v>0</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0</v>
+        <v>0.856321</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0</v>
+        <v>0.671803</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0</v>
+        <v>0.562963</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0</v>
+        <v>0.63208</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0</v>
+        <v>0.557449</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0</v>
+        <v>0.574724</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0</v>
+        <v>1.23939</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>0</v>
+        <v>1.047141</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>0</v>
+        <v>0.926512</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>0</v>
+        <v>1.550683</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>0</v>
+        <v>1.523796</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>0</v>
+        <v>1.531585</v>
       </c>
       <c r="R68" s="3" t="n">
-        <v>0</v>
+        <v>1.421166</v>
       </c>
       <c r="S68" s="3" t="n">
-        <v>0</v>
+        <v>0.491473</v>
       </c>
     </row>
     <row r="69">
@@ -5282,46 +5282,46 @@
         <v>4.116972</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>4.473478</v>
+        <v>3.617157</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>4.81491</v>
+        <v>4.143107</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>3.965305</v>
+        <v>3.402342</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>5.417925</v>
+        <v>4.785845</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>3.782713</v>
+        <v>3.225264</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>4.603871</v>
+        <v>4.029147</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>6.759945</v>
+        <v>5.520555</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>8.493646999999999</v>
+        <v>7.446506</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>8.998307</v>
+        <v>8.071795</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>3.554356</v>
+        <v>2.003673</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>13.960842</v>
+        <v>12.437046</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>16.807843</v>
+        <v>15.276258</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>17.322637</v>
+        <v>15.901471</v>
       </c>
       <c r="S75" s="3" t="n">
-        <v>4.922266</v>
+        <v>4.430793</v>
       </c>
     </row>
     <row r="76">
@@ -7652,7 +7652,7 @@
         <v>0</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.140721</v>
       </c>
       <c r="F110" s="1" t="inlineStr">
         <is>
@@ -7665,13 +7665,13 @@
         </is>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.011489</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.012341</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.011345</v>
       </c>
       <c r="K110" s="1" t="inlineStr">
         <is>
@@ -21404,7 +21404,11 @@
           <t>Accretion expenses (note 12)</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -24094,7 +24098,11 @@
           <t>Accretion expenses</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
@@ -29586,7 +29594,11 @@
           <t>Director fees (note 21)</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -31592,7 +31604,11 @@
           <t>Director fees (note 20)</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -36314,7 +36330,11 @@
           <t>Director fees (note 19)</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -39838,7 +39858,11 @@
           <t>Director fees (note 18)</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
@@ -43000,7 +43024,11 @@
           <t>Director fees</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
